--- a/attendance_log.xlsx
+++ b/attendance_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,182 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MayBach</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:06:49</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MayBach</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:07:20</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MayBach</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:07:53</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MayBach</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:32:21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:46:02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>17:15:03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MayBach</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:22:44</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sarkodie</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:22:44</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance_log.xlsx
+++ b/attendance_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,6 +966,94 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12:38:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>13:43:26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>13:44:03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>joel</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>14:13:34</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
